--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486693_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486693_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7117</v>
+        <v>5.9655</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8175</v>
+        <v>3.8726</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8942</v>
+        <v>2.0929</v>
       </c>
       <c r="G2" t="n">
         <v>4.2927</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0331</v>
+        <v>0.2207</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2756</v>
+        <v>0.3307</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3087</v>
+        <v>-0.11</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2856</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4471</v>
+        <v>3.4392</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0537</v>
+        <v>0.9712</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3934</v>
+        <v>2.468</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.3177</v>
+        <v>2.7772</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.2205</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09719999999999999</v>
+        <v>1.8674</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.6269</v>
+        <v>1.9231</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.3232</v>
+        <v>-0.6067</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6963</v>
+        <v>2.5298</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3092</v>
+        <v>0.8541</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1027</v>
+        <v>1.5165</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7935</v>
+        <v>-0.6624</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1239</v>
+        <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1324</v>
+        <v>0.345</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3305</v>
+        <v>0.2066</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1981</v>
+        <v>0.1384</v>
       </c>
       <c r="V3" t="n">
-        <v>5.4394</v>
+        <v>-1.2277</v>
       </c>
       <c r="W3" t="n">
-        <v>7.2809</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8415</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9333</v>
+        <v>3.4044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1094</v>
+        <v>3.0606</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8239</v>
+        <v>0.3438</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1069</v>
+        <v>-2.3177</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9036999999999999</v>
+        <v>-2.2205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0105</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0735</v>
+        <v>-2.6269</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5595</v>
+        <v>-3.3232</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.486</v>
+        <v>0.6963</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1803</v>
+        <v>0.3092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3442</v>
+        <v>1.1027</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5245</v>
+        <v>-0.7935</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1239</v>
+        <v>-1.9308</v>
       </c>
       <c r="R4" t="n">
-        <v>2.51</v>
+        <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8551</v>
+        <v>0.0897</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6891</v>
+        <v>0.3374</v>
       </c>
       <c r="U4" t="n">
-        <v>0.166</v>
+        <v>-0.2477</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7989</v>
+        <v>5.4394</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4707</v>
+        <v>7.2809</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3282</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.791</v>
+        <v>2.6644</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.0353</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7163</v>
+        <v>2.6997</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7772</v>
+        <v>-0.1069</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8674</v>
+        <v>-1.0105</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9231</v>
+        <v>0.0735</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6067</v>
+        <v>0.5595</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5298</v>
+        <v>-0.486</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8541</v>
+        <v>-0.1803</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5165</v>
+        <v>0.3442</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6624</v>
+        <v>-0.5245</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7031</v>
+        <v>2.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3031</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6898</v>
+        <v>0.5444</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3867</v>
+        <v>0.0418</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2277</v>
+        <v>1.7989</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4707</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.325</v>
+        <v>2.4003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7032</v>
+        <v>1.0411</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6218</v>
+        <v>1.3592</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0209</v>
+        <v>0.3237</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2482</v>
+        <v>0.5453</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.269</v>
+        <v>-0.2216</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0414</v>
+        <v>0.3105</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0414</v>
+        <v>0.2698</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0623</v>
+        <v>0.0132</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2068</v>
+        <v>0.2755</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.269</v>
+        <v>-0.2623</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5736</v>
+        <v>0.7171</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.7307</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0882</v>
+        <v>-0.0136</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2751</v>
+        <v>1.3527</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1586</v>
+        <v>-1.3246</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4337</v>
+        <v>2.6774</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3237</v>
+        <v>-0.6169</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5453</v>
+        <v>-0.393</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2216</v>
+        <v>-0.2239</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3105</v>
+        <v>-0.1052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2698</v>
+        <v>-1.0819</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>0.9766</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0132</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2755</v>
+        <v>0.6889</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2623</v>
+        <v>-1.2005</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9308</v>
+        <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4082</v>
+        <v>0.2552</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4691</v>
+        <v>0.503</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0609</v>
+        <v>-0.2478</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5712</v>
+        <v>0.9421</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5712</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>J. ORAMAS MARTEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1471</v>
+        <v>1.05</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3316</v>
+        <v>0.1127</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4787</v>
+        <v>0.9374</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6169</v>
+        <v>1.4637</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.393</v>
+        <v>-0.3244</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2239</v>
+        <v>1.7882</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1052</v>
+        <v>1.2437</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0819</v>
+        <v>-0.6688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9766</v>
+        <v>1.9125</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5116000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6889</v>
+        <v>0.3443</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2005</v>
+        <v>-0.1244</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0496</v>
+        <v>-0.6068</v>
       </c>
       <c r="T8" t="n">
-        <v>0.496</v>
+        <v>0.0274</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4464</v>
+        <v>-0.6342</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.3129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0945</v>
+        <v>1.041</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7482</v>
+        <v>0.3447</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3463</v>
+        <v>0.6963</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0103</v>
+        <v>-0.0209</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4625</v>
+        <v>0.2482</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4522</v>
+        <v>-0.269</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2504</v>
+        <v>0.0414</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3583</v>
+        <v>0.0414</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1078</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2401</v>
+        <v>-0.0623</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8958</v>
+        <v>0.2068</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.269</v>
       </c>
       <c r="P9" t="n">
         <v>0.7723</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2814</v>
+        <v>0.2896</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5512</v>
+        <v>0.3033</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8326</v>
+        <v>-0.0137</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7989</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8365</v>
+        <v>0.6796</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1972</v>
+        <v>0.1346</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0337</v>
+        <v>0.545</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4005</v>
+        <v>-0.0103</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5791</v>
+        <v>-0.4625</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1786</v>
+        <v>0.4522</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6202</v>
+        <v>-0.2504</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.7852</v>
+        <v>-1.3583</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1651</v>
+        <v>1.1078</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2197</v>
+        <v>0.2401</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2061</v>
+        <v>0.8958</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0135</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1585</v>
+        <v>-1.3515</v>
       </c>
       <c r="R10" t="n">
-        <v>2.51</v>
+        <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5999</v>
+        <v>-0.6963</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2959</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>0.304</v>
+        <v>-0.6339</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>1.7989</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ORAMAS MARTEL</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3825</v>
+        <v>-0.0944</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3562</v>
+        <v>-2.7556</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7387</v>
+        <v>2.6612</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4637</v>
+        <v>-2.4005</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3244</v>
+        <v>-2.5791</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7882</v>
+        <v>0.1786</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2437</v>
+        <v>-2.6202</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6688</v>
+        <v>-2.7852</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9125</v>
+        <v>0.1651</v>
       </c>
       <c r="M11" t="n">
-        <v>0.22</v>
+        <v>0.2197</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3443</v>
+        <v>0.2061</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1244</v>
+        <v>0.0135</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3515</v>
+        <v>2.51</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2743</v>
+        <v>0.669</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4415</v>
+        <v>0.7375</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8328</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9046</v>
+        <v>-0.5377</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9481</v>
+        <v>-1.6309</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0435</v>
+        <v>1.0931</v>
       </c>
       <c r="G12" t="n">
         <v>2.1336</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0149</v>
+        <v>-0.648</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4966</v>
+        <v>-0.1794</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5182</v>
+        <v>-0.4686</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1923</v>
+        <v>-1.1386</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8694</v>
+        <v>-1.766</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6771</v>
+        <v>0.6274</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8283</v>
@@ -1468,13 +1468,13 @@
         <v>0.7723</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.171</v>
+        <v>-0.1172</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2759</v>
+        <v>-0.1725</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1049</v>
+        <v>0.0552</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.8469</v>
+        <v>20.2264</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6456999999999995</v>
+        <v>2.025100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>18.2013</v>
+        <v>18.2014</v>
       </c>
       <c r="G14" t="n">
-        <v>4.689400000000001</v>
+        <v>4.689399999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-1.3803</v>
       </c>
       <c r="I14" t="n">
-        <v>6.070199999999999</v>
+        <v>6.070200000000001</v>
       </c>
       <c r="J14" t="n">
         <v>2.7342</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.925400000000001</v>
+        <v>-7.9254</v>
       </c>
       <c r="L14" t="n">
         <v>10.6595</v>
@@ -1543,25 +1543,25 @@
         <v>-14.4809</v>
       </c>
       <c r="R14" t="n">
-        <v>22.20400000000001</v>
+        <v>22.204</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2753999999999999</v>
+        <v>1.1042</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9272</v>
+        <v>3.3067</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2025</v>
+        <v>-2.2026</v>
       </c>
       <c r="V14" t="n">
-        <v>6.709700000000001</v>
+        <v>6.7097</v>
       </c>
       <c r="W14" t="n">
         <v>10.4652</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.7556</v>
+        <v>-3.755600000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4504</v>
+        <v>2.9897</v>
       </c>
       <c r="E15" t="n">
-        <v>0.417</v>
+        <v>0.5205</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0333</v>
+        <v>2.4692</v>
       </c>
       <c r="G15" t="n">
         <v>4.7468</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7944</v>
+        <v>-0.2551</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2486</v>
+        <v>-0.1452</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5458</v>
+        <v>-0.1099</v>
       </c>
       <c r="V15" t="n">
         <v>0.0426</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1512</v>
+        <v>1.4285</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0783</v>
+        <v>1.1817</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2468</v>
       </c>
       <c r="G16" t="n">
         <v>2.0301</v>
@@ -1702,13 +1702,13 @@
         <v>2.7031</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4359</v>
+        <v>-0.1587</v>
       </c>
       <c r="T16" t="n">
-        <v>0.165</v>
+        <v>0.2684</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6009</v>
+        <v>-0.4271</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0222</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7759</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7496</v>
+        <v>-1.7238</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5255</v>
+        <v>1.1861</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.3653</v>
+        <v>-0.0965</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.6049</v>
+        <v>-0.3723</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2396</v>
+        <v>0.2758</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.2259</v>
+        <v>-0.6481</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.1211</v>
+        <v>-0.6481</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8952</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8606</v>
+        <v>0.5516</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5162</v>
+        <v>0.2758</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.2758</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3169</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
-        <v>2.51</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6035</v>
+        <v>-0.0551</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8125</v>
+        <v>-0.1104</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.209</v>
+        <v>0.0552</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7792</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4881</v>
+        <v>-0.9938</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7238</v>
+        <v>-1.9766</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2357</v>
+        <v>0.9828</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0965</v>
+        <v>0.4296</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3723</v>
+        <v>1.6413</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2758</v>
+        <v>-1.2117</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6481</v>
+        <v>-0.011</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6481</v>
+        <v>0.6762</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.6872</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5516</v>
+        <v>0.4406</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2758</v>
+        <v>0.9651</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2758</v>
+        <v>-0.5245</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3862</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0055</v>
+        <v>0.0206</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1104</v>
+        <v>0.1582</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1049</v>
+        <v>-0.1376</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.506</v>
+        <v>-1.1323</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0608</v>
+        <v>-0.7506</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4451</v>
+        <v>-0.3817</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0578</v>
@@ -1936,13 +1936,13 @@
         <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3255</v>
+        <v>0.0482</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1383</v>
+        <v>0.172</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1872</v>
+        <v>-0.1238</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7366</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9743</v>
+        <v>-1.2829</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9074</v>
+        <v>-2.9215</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9331</v>
+        <v>1.6386</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4296</v>
+        <v>-3.3653</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6413</v>
+        <v>-3.6049</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2117</v>
+        <v>0.2396</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.011</v>
+        <v>-4.2259</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6762</v>
+        <v>-5.1211</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6872</v>
+        <v>0.8952</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4406</v>
+        <v>0.8606</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9651</v>
+        <v>1.5162</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5245</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1585</v>
+        <v>2.3169</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>2.51</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9598</v>
+        <v>0.5447</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7725</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1873</v>
+        <v>-0.096</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2856</v>
+        <v>-0.7792</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2856</v>
+        <v>-1.6361</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0169</v>
+        <v>-1.7551</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.356</v>
+        <v>-2.7355</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3392</v>
+        <v>0.9804</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2628</v>
@@ -2092,13 +2092,13 @@
         <v>2.7031</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3031</v>
+        <v>-0.0413</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7453</v>
+        <v>-0.1247</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4422</v>
+        <v>0.0834</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0648</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6912</v>
+        <v>-2.3271</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7169</v>
+        <v>-0.3032</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9743</v>
+        <v>-2.024</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8552999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0056</v>
+        <v>0.3584</v>
       </c>
       <c r="T22" t="n">
-        <v>0.248</v>
+        <v>0.6617</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2536</v>
+        <v>-0.3033</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2856</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5485</v>
+        <v>-3.0314</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7964</v>
+        <v>-2.2793</v>
       </c>
       <c r="F23" t="n">
         <v>-0.7521</v>
@@ -2248,10 +2248,10 @@
         <v>0.1931</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3862</v>
+        <v>0.131</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4415</v>
+        <v>0.0757</v>
       </c>
       <c r="U23" t="n">
         <v>0.0553</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2095</v>
+        <v>-5.0605</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3248</v>
+        <v>-2.5437</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8847</v>
+        <v>-2.5168</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5306</v>
+        <v>-3.3031</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0544</v>
+        <v>-1.6415</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4763</v>
+        <v>-1.6616</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1232</v>
+        <v>-1.2125</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1232</v>
+        <v>-1.2962</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.0837</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4074</v>
+        <v>-2.0906</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0689</v>
+        <v>-0.3453</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4763</v>
+        <v>-1.7453</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4754</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0242</v>
+        <v>-0.407</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3165</v>
+        <v>-0.3658</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2923</v>
+        <v>-0.0411</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2277</v>
+        <v>-1.3505</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5712</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.79</v>
+        <v>-6.4547</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0608</v>
+        <v>-4.6693</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7292</v>
+        <v>-1.7854</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.3031</v>
+        <v>-2.5306</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6415</v>
+        <v>-1.0544</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6616</v>
+        <v>-1.4763</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2125</v>
+        <v>-1.1232</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2962</v>
+        <v>-1.1232</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0837</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0906</v>
+        <v>-1.4074</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3453</v>
+        <v>0.0689</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7453</v>
+        <v>-1.4763</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-3.4754</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1365</v>
+        <v>0.779</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8829</v>
+        <v>0.972</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2535</v>
+        <v>-0.193</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.3505</v>
+        <v>-1.2277</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.3505</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="26">
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.847</v>
+        <v>-18.1574</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.2012</v>
+        <v>-18.2013</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6457000000000002</v>
+        <v>0.04389999999999983</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.6895</v>
+        <v>-4.689500000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>1.380399999999998</v>
+        <v>1.3804</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.069999999999999</v>
+        <v>-6.07</v>
       </c>
       <c r="J26" t="n">
         <v>-1.9554</v>
@@ -2467,7 +2467,7 @@
         <v>-2.7341</v>
       </c>
       <c r="N26" t="n">
-        <v>7.925499999999998</v>
+        <v>7.925499999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-10.6597</v>
@@ -2482,13 +2482,13 @@
         <v>14.4809</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2752000000000001</v>
+        <v>0.9646999999999999</v>
       </c>
       <c r="T26" t="n">
         <v>2.2025</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.9272</v>
+        <v>-1.2379</v>
       </c>
       <c r="V26" t="n">
         <v>-6.7096</v>
